--- a/Marriage/All_Expenses.xlsx
+++ b/Marriage/All_Expenses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal Stuff\Preparing for Marriage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://analog-my.sharepoint.com/personal/omar_fahmy_analog_com/Documents/Personal Stuff/Marriage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4790C9F9-A75E-4017-AA67-FFE90E9926F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4790C9F9-A75E-4017-AA67-FFE90E9926F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E3AC1A6-3249-4B26-ABC6-D785E1CB1A57}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -687,13 +687,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G152"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -701,7 +701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -709,7 +709,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
@@ -729,10 +729,10 @@
       </c>
       <c r="G4">
         <f>SUM(B:B)</f>
-        <v>657895</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>653635</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
@@ -740,7 +740,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
@@ -748,7 +748,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
@@ -756,7 +756,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>8</v>
       </c>
@@ -764,7 +764,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>9</v>
       </c>
@@ -772,7 +772,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -781,7 +781,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
@@ -790,7 +790,7 @@
         <v>20233</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
@@ -798,7 +798,7 @@
         <v>16150</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>14</v>
       </c>
@@ -807,7 +807,7 @@
         <v>14745</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>16</v>
       </c>
@@ -816,7 +816,7 @@
         <v>14800</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>17</v>
       </c>
@@ -825,7 +825,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>15</v>
       </c>
@@ -833,7 +833,7 @@
         <v>69500</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>18</v>
       </c>
@@ -841,7 +841,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>20</v>
       </c>
@@ -849,7 +849,7 @@
         <v>24332</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>19</v>
       </c>
@@ -857,7 +857,7 @@
         <v>28600</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>31</v>
       </c>
@@ -866,7 +866,7 @@
         <v>22500</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>21</v>
       </c>
@@ -875,7 +875,7 @@
         <v>16137</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>35</v>
       </c>
@@ -884,7 +884,7 @@
         <v>51219.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>22</v>
       </c>
@@ -893,7 +893,7 @@
         <v>12250</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>23</v>
       </c>
@@ -901,7 +901,7 @@
         <v>-13000</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>24</v>
       </c>
@@ -909,7 +909,7 @@
         <v>-50000</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>25</v>
       </c>
@@ -918,7 +918,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>26</v>
       </c>
@@ -927,7 +927,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>27</v>
       </c>
@@ -935,7 +935,7 @@
         <v>8108</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>28</v>
       </c>
@@ -943,7 +943,7 @@
         <v>-2250</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>29</v>
       </c>
@@ -952,7 +952,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>30</v>
       </c>
@@ -961,7 +961,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>32</v>
       </c>
@@ -970,7 +970,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>33</v>
       </c>
@@ -979,7 +979,7 @@
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>34</v>
       </c>
@@ -988,7 +988,7 @@
         <v>6900</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>36</v>
       </c>
@@ -996,7 +996,7 @@
         <v>-5500</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>37</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>38</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>39</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>42</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>40</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>41</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>43</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>44</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>45</v>
       </c>
@@ -1077,15 +1077,15 @@
         <v>635</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B45" s="3">
-        <v>4260</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>47</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>39195</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>48</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>7265</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>49</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>15985</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>50</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>2565</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>51</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>52</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>53</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>22342.5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>60</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>54</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>56</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>55</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>57</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>3988.5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>58</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>124.5</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>59</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>61</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>62</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>63</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>64</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>65</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>3480.5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>66</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>-20000</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>74</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>67</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>68</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>69</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>70</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>71</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
         <v>72</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>-18900</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>73</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>-38000</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>75</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>48500</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>76</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>77</v>
       </c>
@@ -1353,304 +1353,310 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{eaa689b4-8f87-40e0-9c6f-7228de4d754a}" enabled="0" method="" siteId="{eaa689b4-8f87-40e0-9c6f-7228de4d754a}" removed="1"/>
+</clbl:labelList>
 </file>